--- a/data/exemplare.xlsx
+++ b/data/exemplare.xlsx
@@ -397,259 +397,1611 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:P32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>an</v>
+        <v>luna</v>
       </c>
       <c r="B1" t="str">
-        <v>luna</v>
+        <v>zi</v>
       </c>
       <c r="C1" t="str">
-        <v>zi</v>
+        <v>material_general</v>
       </c>
       <c r="D1" t="str">
-        <v>titlu</v>
+        <v>alte_informatii_titlu</v>
       </c>
       <c r="E1" t="str">
-        <v>material_general</v>
+        <v>locul_publicarii</v>
       </c>
       <c r="F1" t="str">
-        <v>alte_informatii_titlu</v>
+        <v>edituri</v>
       </c>
       <c r="G1" t="str">
-        <v>numarul_unei_parti</v>
+        <v>frecventa</v>
       </c>
       <c r="H1" t="str">
-        <v>numerotare_spec_data</v>
+        <v>Nota</v>
       </c>
       <c r="I1" t="str">
-        <v>locul_publicarii</v>
+        <v>vedeta_intrare</v>
       </c>
       <c r="J1" t="str">
-        <v>edituri</v>
+        <v>fisier_coperta</v>
       </c>
       <c r="K1" t="str">
-        <v>data_publicarii</v>
+        <v>fisier_pdf</v>
       </c>
       <c r="L1" t="str">
-        <v>frecventa</v>
+        <v>descriere</v>
       </c>
       <c r="M1" t="str">
-        <v>nr_inregistrare_autoritate</v>
+        <v>taguri</v>
       </c>
       <c r="N1" t="str">
-        <v>vedeta_intrare</v>
+        <v>j-cota</v>
       </c>
       <c r="O1" t="str">
-        <v>fisier_coperta</v>
+        <v>status</v>
       </c>
       <c r="P1" t="str">
-        <v>fisier_pdf</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>denumire_completa</v>
-      </c>
-      <c r="R1" t="str">
-        <v>descriere</v>
-      </c>
-      <c r="S1" t="str">
-        <v>taguri</v>
-      </c>
-      <c r="T1" t="str">
-        <v>status</v>
+        <v>__EMPTY</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1923</v>
+        <v>01</v>
       </c>
       <c r="B2" t="str">
-        <v>01</v>
+        <v>27</v>
       </c>
       <c r="C2" t="str">
-        <v>27</v>
+        <v>periodic</v>
       </c>
       <c r="D2" t="str">
-        <v>Argus</v>
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
       </c>
       <c r="E2" t="str">
-        <v>periodic</v>
+        <v>Bucureşti</v>
       </c>
       <c r="F2" t="str">
-        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+        <v>Atelierele "Adevěrul"</v>
       </c>
       <c r="G2" t="str">
-        <v>Anul 14, nr. 2930 (27 Ianuarie 1923)</v>
+        <v>Zilnic</v>
       </c>
       <c r="H2" t="str">
-        <v>Anul XIV, No. 2930, 27 Ianuarie 1923</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>Bucureşti</v>
+        <v>Comerţ</v>
       </c>
       <c r="J2" t="str">
-        <v>Atelierele "Adevěrul"</v>
+        <v>public/1923/coperti/ARGUS_14_1923_2930_page1.jpg</v>
       </c>
       <c r="K2" t="str">
-        <v>1923</v>
+        <v>public/1923/ARGUS_14_1923_2930.pdf</v>
       </c>
       <c r="L2" t="str">
-        <v>Zilnic</v>
+        <v>Periodic</v>
       </c>
       <c r="M2" t="str">
-        <v>109</v>
+        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
       </c>
       <c r="N2" t="str">
-        <v>Comerţ</v>
+        <v>P.IV.2766</v>
       </c>
       <c r="O2" t="str">
-        <v>public/1923/coperti/ARGUS_14_1923_2930_page1.jpg</v>
+        <v>OK</v>
       </c>
       <c r="P2" t="str">
-        <v>public/1923/ARGUS_14_1923_2930.pdf</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>Argus nr. 2930/1923</v>
-      </c>
-      <c r="R2" t="str">
-        <v>Periodic</v>
-      </c>
-      <c r="S2" t="str">
-        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
-      </c>
-      <c r="T2" t="str">
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>1923</v>
+        <v>01</v>
       </c>
       <c r="B3" t="str">
-        <v>01</v>
+        <v>28</v>
       </c>
       <c r="C3" t="str">
-        <v>28</v>
+        <v>periodic</v>
       </c>
       <c r="D3" t="str">
-        <v>Argus</v>
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
       </c>
       <c r="E3" t="str">
-        <v>periodic</v>
+        <v>Bucureşti</v>
       </c>
       <c r="F3" t="str">
-        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+        <v>Atelierele "Adevěrul"</v>
       </c>
       <c r="G3" t="str">
-        <v>Anul 14, nr. 2931 (28 Ianuarie 1923)</v>
+        <v>Zilnic</v>
       </c>
       <c r="H3" t="str">
-        <v>Anul XIV, No. 2931, 28 Ianuarie 1923</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>Bucureşti</v>
+        <v>Comerţ</v>
       </c>
       <c r="J3" t="str">
-        <v>Atelierele "Adevěrul"</v>
+        <v>public/1923/coperti/ARGUS_14_1923_2931_page1.jpg</v>
       </c>
       <c r="K3" t="str">
-        <v>1923</v>
+        <v>public/1923/ARGUS_14_1923_2931.pdf</v>
       </c>
       <c r="L3" t="str">
-        <v>Zilnic</v>
+        <v>Periodic</v>
       </c>
       <c r="M3" t="str">
-        <v>109</v>
+        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
       </c>
       <c r="N3" t="str">
-        <v>Comerţ</v>
+        <v>P.IV.2766</v>
       </c>
       <c r="O3" t="str">
-        <v>public/1923/coperti/ARGUS_14_1923_2931_page1.jpg</v>
+        <v>OK</v>
       </c>
       <c r="P3" t="str">
-        <v>public/1923/ARGUS_14_1923_2931.pdf</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Argus nr. 2931/1923</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Periodic</v>
-      </c>
-      <c r="S3" t="str">
-        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
-      </c>
-      <c r="T3" t="str">
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1923</v>
+        <v>01</v>
       </c>
       <c r="B4" t="str">
+        <v>29</v>
+      </c>
+      <c r="C4" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D4" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Comerţ</v>
+      </c>
+      <c r="J4" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2932_page1.jpg</v>
+      </c>
+      <c r="K4" t="str">
+        <v>public/1923/ARGUS_14_1923_2932.pdf</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="N4" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O4" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>01</v>
       </c>
-      <c r="C4" t="str">
-        <v>29</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Argus</v>
-      </c>
-      <c r="E4" t="str">
-        <v>periodic</v>
-      </c>
-      <c r="F4" t="str">
-        <v>organ zilnic al comerţului, industriei şi finanţei</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Anul 14, nr. 2932 (29 Ianuarie 1923)</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Anul XIV, No. 2932, 29 Ianuarie 1923</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Bucureşti</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Atelierele "Adevěrul"</v>
-      </c>
-      <c r="K4" t="str">
-        <v>1923</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Zilnic</v>
-      </c>
-      <c r="M4" t="str">
-        <v>109</v>
-      </c>
-      <c r="N4" t="str">
+      <c r="B5">
+        <v>31</v>
+      </c>
+      <c r="C5" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D5" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>Comerţ</v>
       </c>
-      <c r="O4" t="str">
-        <v>public/1923/coperti/ARGUS_14_1923_2932_page1.jpg</v>
-      </c>
-      <c r="P4" t="str">
-        <v>public/1923/ARGUS_14_1923_2932.pdf</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>Argus nr. 2932/1923</v>
-      </c>
-      <c r="R4" t="str">
-        <v>Periodic</v>
-      </c>
-      <c r="S4" t="str">
+      <c r="J5" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2933_page1.jpg</v>
+      </c>
+      <c r="K5" t="str">
+        <v>public/1923/ARGUS_14_1923_2933.pdf</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M5" t="str">
         <v>Organ zilnic al comerţului, industriei şi finanţei</v>
       </c>
-      <c r="T4" t="str">
-        <v>OK</v>
+      <c r="N5" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O5" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>02</v>
+      </c>
+      <c r="B6" t="str">
+        <v>01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D6" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Comerţ</v>
+      </c>
+      <c r="J6" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2934_page1.jpg</v>
+      </c>
+      <c r="K6" t="str">
+        <v>public/1923/ARGUS_14_1923_2934.pdf</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="N6" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O6" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>02</v>
+      </c>
+      <c r="B7" t="str">
+        <v>02</v>
+      </c>
+      <c r="C7" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D7" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Comerţ</v>
+      </c>
+      <c r="J7" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2935_page1.jpg</v>
+      </c>
+      <c r="K7" t="str">
+        <v>public/1923/ARGUS_14_1923_2935.pdf</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="N7" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O7" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>02</v>
+      </c>
+      <c r="B8" t="str">
+        <v>03</v>
+      </c>
+      <c r="C8" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D8" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J8" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2936_page1.jpg</v>
+      </c>
+      <c r="K8" t="str">
+        <v>public/1923/ARGUS_14_1923_2936.pdf</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="N8" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O8" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>02</v>
+      </c>
+      <c r="B9" t="str">
+        <v>04</v>
+      </c>
+      <c r="C9" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D9" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J9" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2937_page1.jpg</v>
+      </c>
+      <c r="K9" t="str">
+        <v>public/1923/ARGUS_14_1923_2937.pdf</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="N9" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O9" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>02</v>
+      </c>
+      <c r="B10" t="str">
+        <v>05</v>
+      </c>
+      <c r="C10" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D10" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J10" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2938_page1.jpg</v>
+      </c>
+      <c r="K10" t="str">
+        <v>public/1923/ARGUS_14_1923_2938.pdf</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="N10" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O10" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>02</v>
+      </c>
+      <c r="B11" t="str">
+        <v>07</v>
+      </c>
+      <c r="C11" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D11" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J11" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2939_page1.jpg</v>
+      </c>
+      <c r="K11" t="str">
+        <v>public/1923/ARGUS_14_1923_2939.pdf</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="N11" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O11" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>02</v>
+      </c>
+      <c r="B12" t="str">
+        <v>09</v>
+      </c>
+      <c r="C12" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D12" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J12" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2940_page1.jpg</v>
+      </c>
+      <c r="K12" t="str">
+        <v>public/1923/ARGUS_14_1923_2940.pdf</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N12" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O12" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>02</v>
+      </c>
+      <c r="B13" t="str">
+        <v>10</v>
+      </c>
+      <c r="C13" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D13" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J13" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2941_page1.jpg</v>
+      </c>
+      <c r="K13" t="str">
+        <v>public/1923/ARGUS_14_1923_2941.pdf</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N13" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O13" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>02</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D14" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E14" t="str">
+        <v>[Bucureşti]</v>
+      </c>
+      <c r="F14" t="str">
+        <v>[s.n.]</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J14" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2942_page1.jpg</v>
+      </c>
+      <c r="K14" t="str">
+        <v>public/1923/ARGUS_14_1923_2942.pdf</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N14" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O14" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>02</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D15" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J15" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2943_page1.jpg</v>
+      </c>
+      <c r="K15" t="str">
+        <v>public/1923/ARGUS_14_1923_2943.pdf</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N15" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O15" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>02</v>
+      </c>
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D16" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J16" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2944_page1.jpg</v>
+      </c>
+      <c r="K16" t="str">
+        <v>public/1923/ARGUS_14_1923_2944.pdf</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N16" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O16" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>02</v>
+      </c>
+      <c r="B17" t="str">
+        <v>15</v>
+      </c>
+      <c r="C17" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D17" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J17" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2945_page1.jpg</v>
+      </c>
+      <c r="K17" t="str">
+        <v>public/1923/ARGUS_14_1923_2945.pdf</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N17" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O17" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>02</v>
+      </c>
+      <c r="B18" t="str">
+        <v>16</v>
+      </c>
+      <c r="C18" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D18" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J18" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2946_page1.jpg</v>
+      </c>
+      <c r="K18" t="str">
+        <v>public/1923/ARGUS_14_1923_2946.pdf</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N18" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O18" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>02</v>
+      </c>
+      <c r="B19" t="str">
+        <v>17</v>
+      </c>
+      <c r="C19" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D19" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E19" t="str">
+        <v>[Bucureşti]</v>
+      </c>
+      <c r="F19" t="str">
+        <v>[s.n.]</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J19" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2947_page1.jpg</v>
+      </c>
+      <c r="K19" t="str">
+        <v>public/1923/ARGUS_14_1923_2947.pdf</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N19" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O19" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>02</v>
+      </c>
+      <c r="B20" t="str">
+        <v>18</v>
+      </c>
+      <c r="C20" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D20" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J20" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2948_page1.jpg</v>
+      </c>
+      <c r="K20" t="str">
+        <v>public/1923/ARGUS_14_1923_2948.pdf</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N20" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O20" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>02</v>
+      </c>
+      <c r="B21" t="str">
+        <v>19</v>
+      </c>
+      <c r="C21" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D21" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J21" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2949_page1.jpg</v>
+      </c>
+      <c r="K21" t="str">
+        <v>public/1923/ARGUS_14_1923_2949.pdf</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N21" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O21" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>02</v>
+      </c>
+      <c r="B22" t="str">
+        <v>21</v>
+      </c>
+      <c r="C22" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D22" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J22" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2950_page1.jpg</v>
+      </c>
+      <c r="K22" t="str">
+        <v>public/1923/ARGUS_14_1923_2950.pdf</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N22" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O22" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>02</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D23" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J23" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2951_page1.jpg</v>
+      </c>
+      <c r="K23" t="str">
+        <v>public/1923/ARGUS_14_1923_2951.pdf</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N23" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O23" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>02</v>
+      </c>
+      <c r="B24" t="str">
+        <v>22</v>
+      </c>
+      <c r="C24" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D24" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J24" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2952_page1.jpg</v>
+      </c>
+      <c r="K24" t="str">
+        <v>public/1923/ARGUS_14_1923_2952.pdf</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N24" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O24" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>02</v>
+      </c>
+      <c r="B25" t="str">
+        <v>24</v>
+      </c>
+      <c r="C25" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D25" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J25" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2953_page1.jpg</v>
+      </c>
+      <c r="K25" t="str">
+        <v>public/1923/ARGUS_14_1923_2953.pdf</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N25" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O25" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>02</v>
+      </c>
+      <c r="B26" t="str">
+        <v>25</v>
+      </c>
+      <c r="C26" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D26" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J26" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2954_page1.jpg</v>
+      </c>
+      <c r="K26" t="str">
+        <v>public/1923/ARGUS_14_1923_2954.pdf</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N26" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O26" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>02</v>
+      </c>
+      <c r="B27" t="str">
+        <v>26</v>
+      </c>
+      <c r="C27" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D27" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J27" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2955_page1.jpg</v>
+      </c>
+      <c r="K27" t="str">
+        <v>public/1923/ARGUS_14_1923_2955.pdf</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N27" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O27" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>02</v>
+      </c>
+      <c r="B28" t="str">
+        <v>28</v>
+      </c>
+      <c r="C28" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D28" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J28" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2956_page1.jpg</v>
+      </c>
+      <c r="K28" t="str">
+        <v>public/1923/ARGUS_14_1923_2956.pdf</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N28" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O28" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>03</v>
+      </c>
+      <c r="B29" t="str">
+        <v>01</v>
+      </c>
+      <c r="C29" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D29" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J29" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2957_page1.jpg</v>
+      </c>
+      <c r="K29" t="str">
+        <v>public/1923/ARGUS_14_1923_2957.pdf</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N29" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O29" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>03</v>
+      </c>
+      <c r="B30" t="str">
+        <v>02</v>
+      </c>
+      <c r="C30" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D30" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J30" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2958_page1.jpg</v>
+      </c>
+      <c r="K30" t="str">
+        <v>public/1923/ARGUS_14_1923_2958.pdf</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N30" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O30" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>03</v>
+      </c>
+      <c r="B31" t="str">
+        <v>03</v>
+      </c>
+      <c r="C31" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D31" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J31" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2959_page1.jpg</v>
+      </c>
+      <c r="K31" t="str">
+        <v>public/1923/ARGUS_14_1923_2959.pdf</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N31" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O31" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>03</v>
+      </c>
+      <c r="B32" t="str">
+        <v>04</v>
+      </c>
+      <c r="C32" t="str">
+        <v>periodic</v>
+      </c>
+      <c r="D32" t="str">
+        <v>organ zilnic al comerţului, industriei şi finanţei</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Bucureşti</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Atelierele "Adevěrul"</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Zilnic</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="J32" t="str">
+        <v>public/1923/coperti/ARGUS_14_1923_2960_page1.jpg</v>
+      </c>
+      <c r="K32" t="str">
+        <v>public/1923/ARGUS_14_1923_2960.pdf</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Periodic</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Comerţ,Industrie,Informații generale</v>
+      </c>
+      <c r="N32" t="str">
+        <v>P.IV.2766</v>
+      </c>
+      <c r="O32" t="str">
+        <v>OK</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P32"/>
   </ignoredErrors>
 </worksheet>
 </file>